--- a/artfynd/A 43326-2025 artfynd.xlsx
+++ b/artfynd/A 43326-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130367160</v>
+        <v>130367179</v>
       </c>
       <c r="B3" t="n">
         <v>57839</v>
@@ -879,22 +879,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 43326-2025 artfynd.xlsx
+++ b/artfynd/A 43326-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130367239</v>
       </c>
       <c r="B2" t="n">
-        <v>57983</v>
+        <v>58009</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,10 +798,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130367179</v>
+        <v>130367160</v>
       </c>
       <c r="B3" t="n">
-        <v>57839</v>
+        <v>57865</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -879,22 +879,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,7 +924,7 @@
         <v>130367330</v>
       </c>
       <c r="B4" t="n">
-        <v>58546</v>
+        <v>58572</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>130436477</v>
       </c>
       <c r="B5" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 43326-2025 artfynd.xlsx
+++ b/artfynd/A 43326-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130367239</v>
       </c>
       <c r="B2" t="n">
-        <v>58009</v>
+        <v>58011</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,10 +798,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130367179</v>
+        <v>130367160</v>
       </c>
       <c r="B3" t="n">
-        <v>57865</v>
+        <v>57867</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -879,22 +879,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,7 +924,7 @@
         <v>130367330</v>
       </c>
       <c r="B4" t="n">
-        <v>58572</v>
+        <v>58574</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>130436477</v>
       </c>
       <c r="B5" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 43326-2025 artfynd.xlsx
+++ b/artfynd/A 43326-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130367239</v>
       </c>
       <c r="B2" t="n">
-        <v>58011</v>
+        <v>58019</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>130367160</v>
       </c>
       <c r="B3" t="n">
-        <v>57867</v>
+        <v>57875</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>130367330</v>
       </c>
       <c r="B4" t="n">
-        <v>58574</v>
+        <v>58582</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>130436477</v>
       </c>
       <c r="B5" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 43326-2025 artfynd.xlsx
+++ b/artfynd/A 43326-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130367239</v>
       </c>
       <c r="B2" t="n">
-        <v>58019</v>
+        <v>58020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>130367160</v>
       </c>
       <c r="B3" t="n">
-        <v>57875</v>
+        <v>57876</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>130367330</v>
       </c>
       <c r="B4" t="n">
-        <v>58582</v>
+        <v>58583</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>130436477</v>
       </c>
       <c r="B5" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 43326-2025 artfynd.xlsx
+++ b/artfynd/A 43326-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130367239</v>
       </c>
       <c r="B2" t="n">
-        <v>58020</v>
+        <v>58021</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>130367160</v>
       </c>
       <c r="B3" t="n">
-        <v>57876</v>
+        <v>57877</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>130367330</v>
       </c>
       <c r="B4" t="n">
-        <v>58583</v>
+        <v>58584</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>130436477</v>
       </c>
       <c r="B5" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 43326-2025 artfynd.xlsx
+++ b/artfynd/A 43326-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130367160</v>
+        <v>130367179</v>
       </c>
       <c r="B3" t="n">
         <v>57877</v>
@@ -879,22 +879,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 43326-2025 artfynd.xlsx
+++ b/artfynd/A 43326-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130367239</v>
+        <v>130367160</v>
       </c>
       <c r="B2" t="n">
-        <v>58021</v>
+        <v>57966</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103020</v>
+        <v>100048</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -798,27 +798,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130367179</v>
+        <v>130436477</v>
       </c>
       <c r="B3" t="n">
-        <v>57877</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100048</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -889,12 +889,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -921,10 +921,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130367330</v>
+        <v>128498431</v>
       </c>
       <c r="B4" t="n">
-        <v>58584</v>
+        <v>58112</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -932,21 +932,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103055</v>
+        <v>103020</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -954,28 +954,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Olofslundsvägen, Sk</t>
+          <t>Entita Oloflundsvägen, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>379201</v>
+        <v>379254</v>
       </c>
       <c r="R4" t="n">
-        <v>6207918</v>
+        <v>6207830</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1002,22 +998,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,22 +1018,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Karl-Erik Söderqvist</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Karl-Erik Söderqvist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130436477</v>
+        <v>130367193</v>
       </c>
       <c r="B5" t="n">
-        <v>57875</v>
+        <v>58112</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1055,16 +1041,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103020</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1130,7 +1116,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1140,7 +1126,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1164,6 +1150,129 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130367330</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Olofslundsvägen, Sk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>379201</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6207918</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Svalöv</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Kågeröd</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Thomas Arnström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Thomas Arnström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43326-2025 artfynd.xlsx
+++ b/artfynd/A 43326-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -795,6 +800,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130367160</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -918,6 +928,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130436477</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1027,6 +1042,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128498431</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1150,6 +1170,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130367193</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1273,8 +1298,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130367330</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>